--- a/SGC-CKN/Excel/9779c36a-472a-4bfa-8798-986f947b628a_Lô_CT-02_P1-10_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/9779c36a-472a-4bfa-8798-986f947b628a_Lô_CT-02_P1-10_D800_06-04-2026.xlsx
@@ -1152,7 +1152,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-3.6</v>
@@ -1161,10 +1161,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" s="5">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="J11" s="8">
-        <v>3.47</v>
+        <v>4.32</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1400,16 +1400,16 @@
         <v>-34</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.6</v>
+        <v>-44.65</v>
       </c>
       <c r="H18" s="28">
         <v>1.05</v>
       </c>
       <c r="I18" s="28">
-        <v>10.6</v>
+        <v>10.65</v>
       </c>
       <c r="J18" s="12">
-        <v>10.1</v>
+        <v>10.14</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>34</v>
@@ -1564,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-3.6</v>
@@ -1573,10 +1573,10 @@
         <v>0.83</v>
       </c>
       <c r="H2" s="5">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="I2" s="8">
-        <v>3.47</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1770,16 +1770,16 @@
         <v>-34</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.6</v>
+        <v>-44.65</v>
       </c>
       <c r="G9" s="28">
         <v>1.05</v>
       </c>
       <c r="H9" s="28">
-        <v>10.6</v>
+        <v>10.65</v>
       </c>
       <c r="I9" s="12">
-        <v>10.1</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1796,19 +1796,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.6</v>
+        <v>-44.65</v>
       </c>
       <c r="G10" s="33">
         <v>7.83</v>
       </c>
       <c r="H10" s="33">
-        <v>43.89</v>
+        <v>44.65</v>
       </c>
       <c r="I10" s="33">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
